--- a/src/test/resources/test-plan.xlsx
+++ b/src/test/resources/test-plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://haagahelia.sharepoint.com/teams/Nat20/Jaetut asiakirjat/General/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://haagahelia-my.sharepoint.com/personal/bhi277_myy_haaga-helia_fi/Documents/Ohjelmistoprojekti 2/kamppis-server/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{AA401EEB-94A2-43D2-BD51-4687DDB1FCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE76FCB0-7D3B-49CF-98F6-922127680DDB}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{AA401EEB-94A2-43D2-BD51-4687DDB1FCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA0F4567-68FE-421B-8599-52E05152845C}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{433FBE55-D699-4420-9B6B-32D27DFE03B9}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{433FBE55-D699-4420-9B6B-32D27DFE03B9}"/>
   </bookViews>
   <sheets>
     <sheet name="And To Start With" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="76">
   <si>
     <t>Name</t>
   </si>
@@ -252,13 +252,37 @@
   </si>
   <si>
     <t>- Tests that custom annotations @ValidAgePreferences and @ValidFurnishedInfo work as expected</t>
+  </si>
+  <si>
+    <t>- MessageController
+- MessageRepository</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>- Authservice
+- GitHubAuthService</t>
+  </si>
+  <si>
+    <t>- FileSystemStorageService
+- StorageService</t>
+  </si>
+  <si>
+    <t>security</t>
+  </si>
+  <si>
+    <t>storage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,8 +399,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4ABBD558-5F9A-4166-BD68-320462E84AE8}" name="Table1" displayName="Table1" ref="A1:H23" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H23" xr:uid="{4ABBD558-5F9A-4166-BD68-320462E84AE8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4ABBD558-5F9A-4166-BD68-320462E84AE8}" name="Table1" displayName="Table1" ref="A1:H25" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H25" xr:uid="{4ABBD558-5F9A-4166-BD68-320462E84AE8}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{2E81DFD8-1188-43DB-BC08-CAD1F28A391B}" name="Name" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{4EC587E3-D8BE-4DB8-8CDA-AFB85A40D9BE}" name="Description" dataDxfId="6"/>
@@ -708,8 +732,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70202306-7F0C-4C45-A7F3-E957E4195D6D}">
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="34.7109375" customWidth="1"/>
@@ -720,7 +744,7 @@
     <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1">
+    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -746,7 +770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="43.5">
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -770,7 +794,7 @@
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="43.5">
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -792,7 +816,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" ht="43.5">
+    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -816,7 +840,7 @@
       </c>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="43.5">
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -840,7 +864,7 @@
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -862,7 +886,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -886,7 +910,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -908,7 +932,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
@@ -930,7 +954,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" ht="105">
+    <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
@@ -954,7 +978,7 @@
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="105">
+    <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -980,7 +1004,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30">
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
@@ -1002,7 +1026,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" ht="30">
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -1024,7 +1048,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" ht="105">
+    <row r="14" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
@@ -1048,7 +1072,7 @@
       </c>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="90">
+    <row r="15" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>46</v>
       </c>
@@ -1070,14 +1094,16 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30">
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="D16" s="2"/>
       <c r="E16" s="1" t="s">
         <v>48</v>
@@ -1087,10 +1113,10 @@
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>53</v>
       </c>
@@ -1108,7 +1134,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1152,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>56</v>
       </c>
@@ -1146,7 +1172,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -1162,7 +1188,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="45">
+    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>58</v>
       </c>
@@ -1178,7 +1204,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30">
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -1194,7 +1220,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
@@ -1207,6 +1233,46 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1221,7 +1287,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23FA6F-6055-4072-8C8C-3A04D5F9BB23}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="34.7109375" customWidth="1"/>
@@ -1232,7 +1298,7 @@
     <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1">
+    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1258,7 +1324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="45">
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1281,7 +1347,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="45">
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1301,7 +1367,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="45">
+    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -1324,7 +1390,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="45">
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,7 +1413,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1367,7 +1433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -1390,7 +1456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -1410,7 +1476,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
@@ -1430,7 +1496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="105">
+    <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1453,7 +1519,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="105">
+    <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -1476,7 +1542,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30">
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
@@ -1496,7 +1562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30">
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -1516,7 +1582,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="105">
+    <row r="14" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
@@ -1539,7 +1605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="90">
+    <row r="15" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>46</v>
       </c>
@@ -1560,7 +1626,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30">
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -1579,7 +1645,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>53</v>
       </c>
@@ -1596,7 +1662,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>55</v>
       </c>
@@ -1613,7 +1679,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>56</v>
       </c>
@@ -1632,7 +1698,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="60">
+    <row r="20" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>67</v>
       </c>
@@ -1652,15 +1718,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
     </row>
   </sheetData>
@@ -1669,12 +1735,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f5933d67-437a-4d67-b9d3-4c1415568616" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f6bcf209-90b6-4b47-8372-724e8738bc5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1879,24 +1947,48 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f5933d67-437a-4d67-b9d3-4c1415568616" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f6bcf209-90b6-4b47-8372-724e8738bc5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AC02A8-BBB7-4522-9D74-911C998787D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{864FB5C7-6E17-43D6-A83E-1F535EC1DDE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f5933d67-437a-4d67-b9d3-4c1415568616"/>
+    <ds:schemaRef ds:uri="f6bcf209-90b6-4b47-8372-724e8738bc5c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E5A9A36-0623-4BAE-85D8-2F38B3781A03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E5A9A36-0623-4BAE-85D8-2F38B3781A03}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f6bcf209-90b6-4b47-8372-724e8738bc5c"/>
+    <ds:schemaRef ds:uri="f5933d67-437a-4d67-b9d3-4c1415568616"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{864FB5C7-6E17-43D6-A83E-1F535EC1DDE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AC02A8-BBB7-4522-9D74-911C998787D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/test/resources/test-plan.xlsx
+++ b/src/test/resources/test-plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://haagahelia-my.sharepoint.com/personal/bhi277_myy_haaga-helia_fi/Documents/Ohjelmistoprojekti 2/kamppis-server/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{AA401EEB-94A2-43D2-BD51-4687DDB1FCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA0F4567-68FE-421B-8599-52E05152845C}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{AA401EEB-94A2-43D2-BD51-4687DDB1FCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57FC462D-3F92-46AA-96A1-A95054B33482}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{433FBE55-D699-4420-9B6B-32D27DFE03B9}"/>
   </bookViews>
@@ -264,10 +264,6 @@
     <t>Storage</t>
   </si>
   <si>
-    <t>- Authservice
-- GitHubAuthService</t>
-  </si>
-  <si>
     <t>- FileSystemStorageService
 - StorageService</t>
   </si>
@@ -276,6 +272,11 @@
   </si>
   <si>
     <t>storage</t>
+  </si>
+  <si>
+    <t>- Authservice
+- GitHubAuthService
+- UserAuthProviderRepository</t>
   </si>
 </sst>
 </file>
@@ -1236,17 +1237,17 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>12</v>
@@ -1262,11 +1263,11 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>12</v>
@@ -1735,14 +1736,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f5933d67-437a-4d67-b9d3-4c1415568616" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f6bcf209-90b6-4b47-8372-724e8738bc5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1947,21 +1946,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f5933d67-437a-4d67-b9d3-4c1415568616" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f6bcf209-90b6-4b47-8372-724e8738bc5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{864FB5C7-6E17-43D6-A83E-1F535EC1DDE2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AC02A8-BBB7-4522-9D74-911C998787D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f5933d67-437a-4d67-b9d3-4c1415568616"/>
-    <ds:schemaRef ds:uri="f6bcf209-90b6-4b47-8372-724e8738bc5c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1986,9 +1984,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AC02A8-BBB7-4522-9D74-911C998787D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{864FB5C7-6E17-43D6-A83E-1F535EC1DDE2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f5933d67-437a-4d67-b9d3-4c1415568616"/>
+    <ds:schemaRef ds:uri="f6bcf209-90b6-4b47-8372-724e8738bc5c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/src/test/resources/test-plan.xlsx
+++ b/src/test/resources/test-plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://haagahelia-my.sharepoint.com/personal/bhi277_myy_haaga-helia_fi/Documents/Ohjelmistoprojekti 2/kamppis-server/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{AA401EEB-94A2-43D2-BD51-4687DDB1FCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57FC462D-3F92-46AA-96A1-A95054B33482}"/>
+  <xr:revisionPtr revIDLastSave="328" documentId="8_{AA401EEB-94A2-43D2-BD51-4687DDB1FCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5265535-03F6-40B6-8D70-BA4B29D17CB3}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{433FBE55-D699-4420-9B6B-32D27DFE03B9}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{433FBE55-D699-4420-9B6B-32D27DFE03B9}"/>
   </bookViews>
   <sheets>
     <sheet name="And To Start With" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="137">
   <si>
     <t>Name</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>Tests create swipe</t>
-  </si>
-  <si>
-    <t>Ïntegration</t>
   </si>
   <si>
     <t>UserControllerTests</t>
@@ -158,9 +155,6 @@
     <t>QueryServiceTests</t>
   </si>
   <si>
-    <t>No need to test query twice</t>
-  </si>
-  <si>
     <t>SwipeServiceTests</t>
   </si>
   <si>
@@ -242,15 +236,6 @@
     <t>Positive and negative feeds</t>
   </si>
   <si>
-    <t>Age calculation</t>
-  </si>
-  <si>
-    <t>No changes made</t>
-  </si>
-  <si>
-    <t>ValidationServiceTests</t>
-  </si>
-  <si>
     <t>- Tests that custom annotations @ValidAgePreferences and @ValidFurnishedInfo work as expected</t>
   </si>
   <si>
@@ -277,6 +262,239 @@
     <t>- Authservice
 - GitHubAuthService
 - UserAuthProviderRepository</t>
+  </si>
+  <si>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>FeedbackControllerTest</t>
+  </si>
+  <si>
+    <t>FlatControllerTest</t>
+  </si>
+  <si>
+    <t>ImageControllerTest</t>
+  </si>
+  <si>
+    <t>InvitecontrollerTest</t>
+  </si>
+  <si>
+    <t>Uses WebMVC</t>
+  </si>
+  <si>
+    <t>Tests
+- Find all feedbacks
+- Post feedback</t>
+  </si>
+  <si>
+    <t>Tests CRUD methods for Flat</t>
+  </si>
+  <si>
+    <t>Tests get, upload, delete and update image</t>
+  </si>
+  <si>
+    <t>Tests
+- Generating a new invite token (and trying to create a token when it already exists)
+- Joining a room with valid invite (and joining a room with expired invite or with user that's already been added)</t>
+  </si>
+  <si>
+    <t>Tests
+- JWT token generation
+- Accessing protected endpoints with valid token (and without a token or with an expired one)</t>
+  </si>
+  <si>
+    <t>MatchControllerTest</t>
+  </si>
+  <si>
+    <t>LoginControllerTest</t>
+  </si>
+  <si>
+    <t>Tests get and create Match</t>
+  </si>
+  <si>
+    <t>Tests get and update Profile of specific subtype (and throwing 404 when subtype doesn't exist)</t>
+  </si>
+  <si>
+    <t>RoomProfileControllerTest</t>
+  </si>
+  <si>
+    <t>ProfileControllerTest</t>
+  </si>
+  <si>
+    <t>Tests
+- CRUD methods for RoomProfile
+- Query methods</t>
+  </si>
+  <si>
+    <t>UserProfileControllerTest</t>
+  </si>
+  <si>
+    <t>SwipeControllerTest</t>
+  </si>
+  <si>
+    <t>UserControllerTest</t>
+  </si>
+  <si>
+    <t>Tests
+- CRUD methods for UserProfile
+- Query methods</t>
+  </si>
+  <si>
+    <t>Uses @DataJPATest</t>
+  </si>
+  <si>
+    <t>Tests
+- Adding a new User to Match
+- Finding Match by user_id
+- Finding user_profiles that have a Match with a certain User
+- Finding Match by multiple users
+- Finding Match by the users included in specific Match</t>
+  </si>
+  <si>
+    <t>ProfilePhotoRepositoryTest</t>
+  </si>
+  <si>
+    <t>MatchRepositoryTest</t>
+  </si>
+  <si>
+    <t>RoomProfileRepositoryTest</t>
+  </si>
+  <si>
+    <t>UserProfileRepositoryTest</t>
+  </si>
+  <si>
+    <t>FlatServiceTest</t>
+  </si>
+  <si>
+    <t>QueryServiceTest</t>
+  </si>
+  <si>
+    <t>SwipeServiceTest</t>
+  </si>
+  <si>
+    <t>UserProfileServiceTest</t>
+  </si>
+  <si>
+    <t>UserServiceTest</t>
+  </si>
+  <si>
+    <t>ValidationServiceTest</t>
+  </si>
+  <si>
+    <t>ProfileRepositoryTest</t>
+  </si>
+  <si>
+    <t>RoommatePreferenceRepositoryTest</t>
+  </si>
+  <si>
+    <t>RoomPreferenceRepositoryTest</t>
+  </si>
+  <si>
+    <t>RoomProfileInviteRepositoryTest</t>
+  </si>
+  <si>
+    <t>Tests finding all photos associated with a certain Profile</t>
+  </si>
+  <si>
+    <t>Tests finding Profile by status (and returning null if no Profile was found)</t>
+  </si>
+  <si>
+    <t>Tests finding RoommatePreference by status (and returning null if none was found)</t>
+  </si>
+  <si>
+    <t>Tests finding RoomPreference by status (and returning null if none was found)</t>
+  </si>
+  <si>
+    <t>Tests
+- Returning an invite when token is not expired (and returning null when it is)
+- Finding invite by token (and returning null when none was found)</t>
+  </si>
+  <si>
+    <t>Tests
+- Finding by active profiles
+- Finding RoomProfile by User
+- Filtering query results correctly
+- Determining PetHousehold status
+- Finding RoomProfile by UserProfile</t>
+  </si>
+  <si>
+    <t>SwipeRepositoryTest</t>
+  </si>
+  <si>
+    <t>UserRepositoryTest</t>
+  </si>
+  <si>
+    <t>Tests that repository finds right swipes by swiper, swiped, and isRightSwipe = true (and returns null if not)</t>
+  </si>
+  <si>
+    <t>Tests
+- Finding User by email
+- Finding users by status
+- Finding users with a deletedAt value != null
+- Finding users with certain email suffix</t>
+  </si>
+  <si>
+    <t>ContextSetup</t>
+  </si>
+  <si>
+    <t>StandaloneSetup</t>
+  </si>
+  <si>
+    <t>setup</t>
+  </si>
+  <si>
+    <t>Generates repository-dependent test data for repository tests</t>
+  </si>
+  <si>
+    <t>Generates standalone test data for controller and service class tests</t>
+  </si>
+  <si>
+    <t>RoomProfileServiceTest</t>
+  </si>
+  <si>
+    <t>FeedbackServiceTest</t>
+  </si>
+  <si>
+    <t>InviteServiceTest</t>
+  </si>
+  <si>
+    <t>MatchServiceTest</t>
+  </si>
+  <si>
+    <t>ProfileServiceTest</t>
+  </si>
+  <si>
+    <t>Tests find and add methods</t>
+  </si>
+  <si>
+    <t>Tests
+- CRUD methods
+- Methods for updating petHousehold status</t>
+  </si>
+  <si>
+    <t>Tests finding and generating invite token</t>
+  </si>
+  <si>
+    <t>Tests
+- CRUD methods
+- Adding and removing a User from Match
+- Finding profiles that have matched with User</t>
+  </si>
+  <si>
+    <t>Tests finding Profile of specific subtype (and throwing exception when none exists)</t>
+  </si>
+  <si>
+    <t>Tests
+- Returning Page of ProfileDTOs when querying matching profiles
+- Returning all UserProfiles that have swiped a RoomProfile to the right</t>
+  </si>
+  <si>
+    <t>Tests
+- CRUD methods
+- Finding a list of room_profiles associated with certain User</t>
+  </si>
+  <si>
+    <t>Tests add, update, delete, and restore methods</t>
   </si>
 </sst>
 </file>
@@ -320,7 +538,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -335,37 +553,144 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="31">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -386,6 +711,166 @@
       </font>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -400,17 +885,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4ABBD558-5F9A-4166-BD68-320462E84AE8}" name="Table1" displayName="Table1" ref="A1:H25" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4ABBD558-5F9A-4166-BD68-320462E84AE8}" name="Table1" displayName="Table1" ref="A1:H26" totalsRowCount="1" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:H25" xr:uid="{4ABBD558-5F9A-4166-BD68-320462E84AE8}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{2E81DFD8-1188-43DB-BC08-CAD1F28A391B}" name="Name" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{4EC587E3-D8BE-4DB8-8CDA-AFB85A40D9BE}" name="Description" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{2CB10FBF-0BCB-4A9E-B95D-F354DD34220D}" name="Add tests for" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{4907A25E-3422-419C-A42B-B796E5FBF952}" name="Number of tests" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{024B50CD-CC47-4E0E-8410-323D0C99CC1F}" name="Package" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{5072D9D8-B5A6-4AC0-8F3B-514F83A80060}" name="Currently type" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{0B11F253-7B19-4F60-924F-0A958B9F8E68}" name="Should be type" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{3534B60A-E17B-4994-9D3A-DC96C3D3385B}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{2E81DFD8-1188-43DB-BC08-CAD1F28A391B}" name="Name" dataDxfId="28" totalsRowDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{4EC587E3-D8BE-4DB8-8CDA-AFB85A40D9BE}" name="Description" dataDxfId="27" totalsRowDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{2CB10FBF-0BCB-4A9E-B95D-F354DD34220D}" name="Add tests for" dataDxfId="26" totalsRowDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{4907A25E-3422-419C-A42B-B796E5FBF952}" name="Number of tests" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{024B50CD-CC47-4E0E-8410-323D0C99CC1F}" name="Package" dataDxfId="24" totalsRowDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{5072D9D8-B5A6-4AC0-8F3B-514F83A80060}" name="Currently type" dataDxfId="23" totalsRowDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{0B11F253-7B19-4F60-924F-0A958B9F8E68}" name="Should be type" dataDxfId="22" totalsRowDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{3534B60A-E17B-4994-9D3A-DC96C3D3385B}" name="Comment" dataDxfId="21" totalsRowDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{420513EA-7BF0-42AC-9743-7124D696C0FB}" name="Table2" displayName="Table2" ref="A1:G36" totalsRowCount="1" headerRowDxfId="14" dataDxfId="15">
+  <autoFilter ref="A1:G35" xr:uid="{420513EA-7BF0-42AC-9743-7124D696C0FB}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C4B73479-B4A8-4C35-9C0A-F9AF8BA29D7C}" name="Name" dataDxfId="20" totalsRowDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{209D6090-6DCA-4FAB-B760-90E819A5C671}" name="Description" dataDxfId="19" totalsRowDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{9257ECC8-E228-4E22-8417-8F965AB7ECE8}" name="Add tests for"/>
+    <tableColumn id="4" xr3:uid="{A8C1695C-71E7-4846-B3AB-060EDB7C0E3D}" name="Number of tests" totalsRowFunction="sum" totalsRowDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{1CD419CA-6EFC-47A3-8168-8E7B3542477D}" name="Package" dataDxfId="18" totalsRowDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{4D1DCC3E-87F2-48C2-9B4F-FC1F56CDA6EE}" name="Currently type" dataDxfId="17" totalsRowDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{244FBC6C-D6B0-47DF-9777-932EA26240BC}" name="Comment" dataDxfId="16" totalsRowDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -733,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70202306-7F0C-4C45-A7F3-E957E4195D6D}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
@@ -742,7 +1243,7 @@
     <col min="5" max="5" width="10.42578125" customWidth="1"/>
     <col min="6" max="6" width="16.140625" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -790,10 +1291,10 @@
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -814,8 +1315,12 @@
       <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="1"/>
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -836,17 +1341,17 @@
       <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
@@ -860,48 +1365,48 @@
       <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>12</v>
@@ -909,67 +1414,73 @@
       <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="1">
         <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="D10" s="1">
         <v>6</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
@@ -977,23 +1488,25 @@
       <c r="G10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>13</v>
@@ -1002,68 +1515,72 @@
         <v>12</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2">
         <v>7</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>13</v>
@@ -1071,55 +1588,57 @@
       <c r="G14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
         <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1127,155 +1646,168 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1">
+        <f>SUBTOTAL(109,Table1[Number of tests])</f>
+        <v>48</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1287,19 +1819,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E23FA6F-6055-4072-8C8C-3A04D5F9BB23}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="34.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1318,430 +1849,732 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6">
+        <v>4</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6">
+        <v>5</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="6">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="6">
+        <v>5</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="6">
+        <v>5</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="6">
+        <v>7</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="6">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="6">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="6">
+        <v>5</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="6">
+        <v>2</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="6">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="6">
+        <v>2</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="6">
+        <v>4</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="6">
+        <v>7</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="6">
+        <v>2</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="6">
+        <v>7</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="6">
+        <v>7</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="6">
+        <v>2</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="6">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E24" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="6">
+        <v>4</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="6">
+        <v>10</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="6">
+        <v>4</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="6">
+        <v>4</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="6">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="E29" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="6">
+        <v>3</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="6">
+        <v>2</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="7">
+        <v>7</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1">
-        <v>6</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="G32" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6">
         <v>7</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="E33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="1">
-        <v>6</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="1">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="1">
-        <v>2</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="105" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="2">
-        <v>7</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="F33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="E34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="1">
-        <v>7</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="E35" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+      <c r="B36" s="7"/>
+      <c r="D36" s="1">
+        <f>SUBTOTAL(109,Table2[Number of tests])</f>
+        <v>143</v>
+      </c>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f5933d67-437a-4d67-b9d3-4c1415568616" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f6bcf209-90b6-4b47-8372-724e8738bc5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1946,20 +2779,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f5933d67-437a-4d67-b9d3-4c1415568616" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f6bcf209-90b6-4b47-8372-724e8738bc5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AC02A8-BBB7-4522-9D74-911C998787D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{864FB5C7-6E17-43D6-A83E-1F535EC1DDE2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f5933d67-437a-4d67-b9d3-4c1415568616"/>
+    <ds:schemaRef ds:uri="f6bcf209-90b6-4b47-8372-724e8738bc5c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1984,12 +2818,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{864FB5C7-6E17-43D6-A83E-1F535EC1DDE2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AC02A8-BBB7-4522-9D74-911C998787D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f5933d67-437a-4d67-b9d3-4c1415568616"/>
-    <ds:schemaRef ds:uri="f6bcf209-90b6-4b47-8372-724e8738bc5c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>